--- a/data/animals.xlsx
+++ b/data/animals.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Animals'!$A$1:$V$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Animals'!$A$1:$U$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V201"/>
+  <dimension ref="A1:U201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,6 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -678,11 +677,6 @@
           <t>Has snout</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>Has trunk</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -760,7 +754,6 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -842,7 +835,6 @@
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -924,7 +916,6 @@
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1006,7 +997,6 @@
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1088,7 +1078,6 @@
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1170,7 +1159,6 @@
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1248,11 +1236,6 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1334,7 +1317,6 @@
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1416,7 +1398,6 @@
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1494,7 +1475,6 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1576,7 +1556,6 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1658,7 +1637,6 @@
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1740,7 +1718,6 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1822,7 +1799,6 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1900,7 +1876,6 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1978,7 +1953,6 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2056,7 +2030,6 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2134,7 +2107,6 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2212,7 +2184,6 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2290,7 +2261,6 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2368,7 +2338,6 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2450,7 +2419,6 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2532,7 +2500,6 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2610,7 +2577,6 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2692,7 +2658,6 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2774,7 +2739,6 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2856,7 +2820,6 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2934,7 +2897,6 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3012,7 +2974,6 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3090,7 +3051,6 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3172,7 +3132,6 @@
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3258,7 +3217,6 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3340,7 +3298,6 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3418,7 +3375,6 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3496,7 +3452,6 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3574,7 +3529,6 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3652,7 +3606,6 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3726,7 +3679,6 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3804,7 +3756,6 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3878,7 +3829,6 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3952,7 +3902,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4038,7 +3987,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4124,7 +4072,6 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4210,11 +4157,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4300,7 +4242,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4378,7 +4319,6 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4460,7 +4400,6 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4546,7 +4485,6 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4628,7 +4566,6 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4714,7 +4651,6 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4796,7 +4732,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4878,7 +4813,6 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4960,7 +4894,6 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5042,7 +4975,6 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5128,7 +5060,6 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5210,7 +5141,6 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5292,7 +5222,6 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5374,7 +5303,6 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5456,7 +5384,6 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5542,7 +5469,6 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5628,7 +5554,6 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5714,7 +5639,6 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5792,7 +5716,6 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5878,7 +5801,6 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5964,7 +5886,6 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6046,7 +5967,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6128,7 +6048,6 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6210,7 +6129,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6288,7 +6206,6 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6366,7 +6283,6 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6444,7 +6360,6 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6522,7 +6437,6 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6608,7 +6522,6 @@
         </is>
       </c>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6686,7 +6599,6 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6768,7 +6680,6 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6850,7 +6761,6 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6928,7 +6838,6 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7002,7 +6911,6 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7080,7 +6988,6 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7166,7 +7073,6 @@
         </is>
       </c>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7244,7 +7150,6 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7326,7 +7231,6 @@
         </is>
       </c>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7404,7 +7308,6 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7478,7 +7381,6 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7560,7 +7462,6 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7642,7 +7543,6 @@
         </is>
       </c>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7720,7 +7620,6 @@
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7806,7 +7705,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7888,7 +7786,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7966,7 +7863,6 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8048,7 +7944,6 @@
       </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8126,7 +8021,6 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8208,7 +8102,6 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8290,7 +8183,6 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8372,7 +8264,6 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8454,7 +8345,6 @@
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8540,7 +8430,6 @@
         </is>
       </c>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8618,7 +8507,6 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8692,7 +8580,6 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8774,7 +8661,6 @@
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8852,11 +8738,6 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8930,7 +8811,6 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9008,7 +8888,6 @@
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9090,7 +8969,6 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9172,7 +9050,6 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9246,7 +9123,6 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9324,7 +9200,6 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9398,7 +9273,6 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9472,7 +9346,6 @@
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9546,7 +9419,6 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9620,7 +9492,6 @@
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9698,11 +9569,6 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9780,7 +9646,6 @@
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9858,7 +9723,6 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9940,7 +9804,6 @@
         </is>
       </c>
       <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10018,7 +9881,6 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10096,7 +9958,6 @@
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10174,7 +10035,6 @@
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10256,7 +10116,6 @@
         </is>
       </c>
       <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10338,7 +10197,6 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10420,7 +10278,6 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10502,7 +10359,6 @@
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10584,7 +10440,6 @@
       </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10662,7 +10517,6 @@
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10740,7 +10594,6 @@
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10826,7 +10679,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10908,7 +10760,6 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10986,7 +10837,6 @@
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11068,7 +10918,6 @@
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
-      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11146,7 +10995,6 @@
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11228,7 +11076,6 @@
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
-      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11306,7 +11153,6 @@
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11388,7 +11234,6 @@
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11470,7 +11315,6 @@
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11552,7 +11396,6 @@
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11634,7 +11477,6 @@
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11712,7 +11554,6 @@
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11794,7 +11635,6 @@
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
-      <c r="V139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11872,7 +11712,6 @@
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11950,7 +11789,6 @@
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12028,7 +11866,6 @@
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12110,7 +11947,6 @@
       </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12188,7 +12024,6 @@
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12262,7 +12097,6 @@
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12344,7 +12178,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12422,7 +12255,6 @@
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
-      <c r="V147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12504,7 +12336,6 @@
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12586,7 +12417,6 @@
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12668,7 +12498,6 @@
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12750,7 +12579,6 @@
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
-      <c r="V151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12832,7 +12660,6 @@
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12914,7 +12741,6 @@
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
-      <c r="V153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12996,7 +12822,6 @@
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13078,7 +12903,6 @@
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
-      <c r="V155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13164,7 +12988,6 @@
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13250,7 +13073,6 @@
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
-      <c r="V157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13332,7 +13154,6 @@
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13418,7 +13239,6 @@
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13504,7 +13324,6 @@
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13582,7 +13401,6 @@
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13656,7 +13474,6 @@
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13738,7 +13555,6 @@
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13824,7 +13640,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -13906,7 +13721,6 @@
         </is>
       </c>
       <c r="U165" t="inlineStr"/>
-      <c r="V165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13984,7 +13798,6 @@
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14062,7 +13875,6 @@
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
-      <c r="V167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14148,7 +13960,6 @@
         </is>
       </c>
       <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14230,7 +14041,6 @@
         </is>
       </c>
       <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14312,7 +14122,6 @@
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14394,7 +14203,6 @@
       </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14472,7 +14280,6 @@
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14550,7 +14357,6 @@
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
-      <c r="V173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14632,7 +14438,6 @@
         </is>
       </c>
       <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14710,7 +14515,6 @@
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
-      <c r="V175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14784,7 +14588,6 @@
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
-      <c r="V176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -14862,7 +14665,6 @@
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
-      <c r="V177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14944,7 +14746,6 @@
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15026,7 +14827,6 @@
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15108,7 +14908,6 @@
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
-      <c r="V180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15182,7 +14981,6 @@
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
-      <c r="V181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15264,7 +15062,6 @@
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15342,7 +15139,6 @@
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15420,7 +15216,6 @@
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15506,7 +15301,6 @@
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
-      <c r="V185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15588,7 +15382,6 @@
         </is>
       </c>
       <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15666,7 +15459,6 @@
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -15752,7 +15544,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -15834,7 +15625,6 @@
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
-      <c r="V189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -15912,7 +15702,6 @@
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
-      <c r="V190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -15986,7 +15775,6 @@
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -16064,7 +15852,6 @@
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -16142,7 +15929,6 @@
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -16220,7 +16006,6 @@
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16294,7 +16079,6 @@
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -16372,7 +16156,6 @@
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -16450,7 +16233,6 @@
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -16528,11 +16310,6 @@
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -16606,7 +16383,6 @@
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -16684,7 +16460,6 @@
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -16762,11 +16537,10 @@
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V201"/>
-  <dataValidations count="19">
+  <autoFilter ref="A1:U201"/>
+  <dataValidations count="18">
     <dataValidation sqref="C2:C700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$7</formula1>
     </dataValidation>
@@ -16822,9 +16596,6 @@
     <dataValidation sqref="U2:U700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"Yes"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/animals.xlsx
+++ b/data/animals.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Animals'!$A$1:$U$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Animals'!$A$1:$T$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U201"/>
+  <dimension ref="A1:T201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -560,15 +560,14 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -634,45 +633,40 @@
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
+          <t>Appearance</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>Special diet</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Locomotion</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Has wings</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Has horns</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Has tail</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Has shell</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>Has stripes</t>
-        </is>
-      </c>
       <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>Has spots</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Has snout</t>
         </is>
@@ -737,23 +731,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -814,27 +811,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -895,27 +891,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -976,27 +971,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1057,27 +1051,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Walks, Swims, Climbs</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1138,27 +1131,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1219,23 +1211,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1296,27 +1291,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1377,27 +1371,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1458,23 +1451,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1535,27 +1531,30 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1616,27 +1615,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1699,25 +1697,28 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1780,25 +1781,28 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1859,23 +1863,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1938,21 +1945,24 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2015,21 +2025,24 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2092,21 +2105,24 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Climbs</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2167,23 +2183,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2244,23 +2263,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2321,23 +2343,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2398,27 +2423,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2481,25 +2509,28 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2560,23 +2591,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2637,27 +2671,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2718,27 +2755,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2799,27 +2839,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2880,23 +2923,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
         <is>
           <t>Climbs, Walks</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2957,23 +3003,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3034,23 +3083,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3111,27 +3163,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3194,29 +3245,32 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3279,25 +3333,28 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3358,23 +3415,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3435,23 +3495,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3514,21 +3577,24 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3589,23 +3655,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>Hops</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3666,19 +3735,22 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>Climbs</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3739,23 +3811,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>Swims, Burrows</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3816,19 +3891,22 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
         <is>
           <t>Climbs</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3889,19 +3967,22 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3964,25 +4045,28 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4049,29 +4133,32 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4134,25 +4221,28 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4219,25 +4309,28 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4302,23 +4395,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4381,25 +4477,28 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4462,29 +4561,32 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4545,27 +4647,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>Flies, Walks</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4628,29 +4733,32 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Flies, Climbs</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4711,27 +4819,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
         <is>
           <t>Swims, Flies, Walks</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4792,27 +4903,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4873,27 +4987,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
         <is>
           <t>Flies, Hops</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4954,27 +5071,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
         <is>
           <t>Swims, Flies</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5037,29 +5157,32 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Flies, Swims</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5120,27 +5243,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5201,27 +5327,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
         <is>
           <t>Walks, Flies</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5282,27 +5411,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5363,27 +5495,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>Walks, Flies</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5446,29 +5581,32 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5531,29 +5669,32 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5616,29 +5757,32 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5701,21 +5845,24 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5778,29 +5925,32 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5863,29 +6013,32 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Flies, Swims</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5946,23 +6099,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6029,25 +6185,28 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Climbs</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6108,23 +6267,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6189,23 +6351,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
         <is>
           <t>Slithers</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6266,23 +6431,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6343,23 +6511,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
         <is>
           <t>Slithers</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6420,23 +6591,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
         <is>
           <t>Slithers, Swims, Climbs</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6499,29 +6673,28 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>Climbs, Walks</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6582,23 +6755,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
         <is>
           <t>Climbs, Walks</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6659,27 +6835,30 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6740,27 +6919,30 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6821,23 +7003,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6898,19 +7083,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
         <is>
           <t>Hops, Swims</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6971,23 +7159,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7050,29 +7241,28 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7133,23 +7323,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7212,25 +7405,24 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>Hops</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7293,21 +7485,24 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>Hops, Climbs</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7368,19 +7563,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
         <is>
           <t>Hops</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7443,25 +7641,28 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7522,27 +7723,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7603,23 +7803,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7682,25 +7885,28 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -7765,23 +7971,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -7846,23 +8055,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7923,27 +8135,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8004,23 +8215,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8083,25 +8297,28 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8164,25 +8381,28 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8245,25 +8465,28 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8324,27 +8547,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr">
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8407,29 +8629,28 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>Flies, Walks</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8490,23 +8711,26 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
         <is>
           <t>Slithers</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8567,19 +8791,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
         <is>
           <t>Burrows</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8642,25 +8869,28 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8721,23 +8951,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr">
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8798,19 +9031,22 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8871,23 +9107,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8950,25 +9189,28 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9031,25 +9273,28 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9110,19 +9355,22 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr">
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9185,21 +9433,24 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9260,19 +9511,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr">
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9333,19 +9587,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr">
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9406,19 +9663,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr">
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9479,19 +9739,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr">
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9552,23 +9815,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr">
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9629,23 +9895,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr">
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9706,23 +9975,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr">
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9783,27 +10055,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr">
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9864,23 +10135,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
         <is>
           <t>Walks, Climbs, Swims</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9941,23 +10215,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10018,23 +10295,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10095,27 +10375,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr">
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10176,27 +10455,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10257,27 +10539,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10338,27 +10623,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr">
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10419,27 +10707,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10500,23 +10787,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr">
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10577,23 +10867,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr">
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10656,25 +10949,28 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
+      <c r="O127" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr">
+      <c r="T127" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -10741,25 +11037,28 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
+      <c r="O128" t="inlineStr">
         <is>
           <t>Walks, Climbs, Burrows</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
-      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10820,23 +11119,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
         <is>
           <t>Climbs, Walks</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr"/>
-      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10897,27 +11199,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
-      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10978,23 +11283,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11057,25 +11365,28 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
+      <c r="O132" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
-      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11136,23 +11447,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11215,25 +11529,28 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr">
+      <c r="O134" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S134" t="inlineStr"/>
       <c r="T134" t="inlineStr"/>
-      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11294,27 +11611,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr"/>
-      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11375,27 +11695,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
-      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11456,27 +11779,30 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
         <is>
           <t>Walks, Swims</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11537,23 +11863,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11616,25 +11945,28 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
+      <c r="O139" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
-      <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11695,23 +12027,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
-      <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11772,23 +12107,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11849,23 +12187,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
         <is>
           <t>Hops, Burrows</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr"/>
-      <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11926,27 +12267,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr">
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
-      <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12007,23 +12347,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr">
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr"/>
-      <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12084,19 +12427,22 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr">
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr"/>
-      <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12159,21 +12505,24 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr">
+      <c r="O146" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr"/>
-      <c r="U146" t="inlineStr">
+      <c r="T146" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -12238,23 +12587,26 @@
           <t>Fur</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr">
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
-      <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12315,27 +12667,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr">
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
-      <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12396,27 +12751,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr">
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
-      <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12477,27 +12835,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
-      <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12558,27 +12919,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
         <is>
           <t>Flies, Hops</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12639,27 +13003,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
         <is>
           <t>Flies, Hops</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
-      <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12720,27 +13087,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr">
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
         <is>
           <t>Walks, Flies</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
-      <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12801,27 +13171,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr">
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12882,27 +13255,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
         <is>
           <t>Flies, Swims, Walks</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12965,29 +13341,32 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr">
+      <c r="O156" t="inlineStr">
         <is>
           <t>Flies, Swims</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13050,29 +13429,32 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr">
+      <c r="O157" t="inlineStr">
         <is>
           <t>Flies, Swims</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
-      <c r="U157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13133,27 +13515,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr">
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
-      <c r="U158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13216,29 +13601,32 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr">
+      <c r="O159" t="inlineStr">
         <is>
           <t>Flies, Hops</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
-      <c r="U159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13301,29 +13689,32 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr">
+      <c r="O160" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
-      <c r="U160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13386,21 +13777,24 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr">
+      <c r="O161" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
-      <c r="U161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13461,19 +13855,22 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr">
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
-      <c r="U162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13534,27 +13931,30 @@
           <t>Feathers</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13617,25 +14017,28 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
+      <c r="O164" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr"/>
-      <c r="U164" t="inlineStr">
+      <c r="T164" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -13700,27 +14103,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr">
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
         <is>
           <t>Slithers, Swims</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13781,23 +14183,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr">
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
         <is>
           <t>Slithers, Climbs</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
-      <c r="U166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13858,23 +14263,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr">
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
         <is>
           <t>Walks, Swims, Climbs</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
-      <c r="U167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13935,31 +14343,30 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14020,27 +14427,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14101,27 +14507,30 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T170" t="inlineStr"/>
-      <c r="U170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14182,27 +14591,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
         <is>
           <t>Slithers, Swims</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
-      <c r="U171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14263,23 +14671,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
         <is>
           <t>Swims, Walks</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
-      <c r="U172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14342,21 +14753,24 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr">
+      <c r="O173" t="inlineStr">
         <is>
           <t>Hops, Swims</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
-      <c r="U173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14417,27 +14831,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14498,23 +14911,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
-      <c r="U175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14575,19 +14991,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
         <is>
           <t>Hops, Swims</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
-      <c r="U176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -14650,21 +15069,24 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr">
+      <c r="O177" t="inlineStr">
         <is>
           <t>Hops, Climbs</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
       <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14727,25 +15149,28 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr">
+      <c r="O178" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14808,25 +15233,28 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr">
+      <c r="O179" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
-      <c r="U179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14889,25 +15317,28 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr">
+      <c r="O180" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
-      <c r="U180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14968,19 +15399,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr"/>
-      <c r="U181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15043,25 +15477,28 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr">
+      <c r="O182" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
-      <c r="U182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15122,23 +15559,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15199,23 +15639,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15278,29 +15721,28 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr">
+      <c r="O185" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
-      <c r="U185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15361,27 +15803,26 @@
           <t>Scales</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr">
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15442,23 +15883,26 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr">
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
-      <c r="U187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -15521,25 +15965,28 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr">
+      <c r="O188" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
-      <c r="U188" t="inlineStr">
+      <c r="T188" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -15606,25 +16053,28 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr">
+      <c r="O189" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -15685,23 +16135,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr">
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
         <is>
           <t>Hops, Flies</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -15762,19 +16215,22 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr">
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -15835,23 +16291,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr">
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
         <is>
           <t>Walks, Flies</t>
         </is>
       </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
-      <c r="U192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15912,23 +16371,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
-      <c r="U193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15991,21 +16453,24 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr">
+      <c r="O194" t="inlineStr">
         <is>
           <t>Walks, Climbs</t>
         </is>
       </c>
-      <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16066,19 +16531,22 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr">
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
         <is>
           <t>Slithers</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -16139,23 +16607,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr">
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
         <is>
           <t>Walks, Burrows</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -16216,23 +16687,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr">
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
         <is>
           <t>Flies, Walks</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -16293,23 +16767,26 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr">
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
-      <c r="U198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -16370,19 +16847,22 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
-      <c r="U199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -16443,23 +16923,26 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr">
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T200" t="inlineStr"/>
-      <c r="U200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -16520,27 +17003,30 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr">
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
         <is>
           <t>Swims, Burrows</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U201"/>
-  <dataValidations count="18">
+  <autoFilter ref="A1:T201"/>
+  <dataValidations count="17">
     <dataValidation sqref="C2:C700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$A$2:$A$7</formula1>
     </dataValidation>
@@ -16571,12 +17057,12 @@
     <dataValidation sqref="L2:L700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Lists!$J$2:$J$7</formula1>
     </dataValidation>
+    <dataValidation sqref="M2:M700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Lists!$K$2:$K$6</formula1>
+    </dataValidation>
     <dataValidation sqref="B2:B700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>3</formula2>
-    </dataValidation>
-    <dataValidation sqref="O2:O700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"Yes"</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes"</formula1>
@@ -16593,9 +17079,6 @@
     <dataValidation sqref="T2:T700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U700" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"Yes"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16607,7 +17090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16622,6 +17105,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16677,15 +17161,20 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Appearance</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>Special diet</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Locomotion</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Fame</t>
         </is>
@@ -16744,15 +17233,20 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Plain</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Insectivore</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Walks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1 = Familiar</t>
         </is>
@@ -16811,15 +17305,20 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Striped</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Piscivore</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Swims</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2 = Known</t>
         </is>
@@ -16878,15 +17377,20 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Spotted</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>Frugivore</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Flies</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>3 = Obscure</t>
         </is>
@@ -16928,7 +17432,12 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Patterned</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Climbs</t>
         </is>
@@ -16965,7 +17474,12 @@
           <t>Exoskeleton</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Multi-colored</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Burrows</t>
         </is>
@@ -16992,7 +17506,7 @@
           <t>Smooth skin</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Hops</t>
         </is>
@@ -17009,7 +17523,7 @@
           <t>Ocean</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Slithers</t>
         </is>
